--- a/APM_files/152672346/152672346 IMPORT RT&RP Custom Label Update.xlsx
+++ b/APM_files/152672346/152672346 IMPORT RT&RP Custom Label Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darkesthj/Dev/workspace/APM_files/152672346/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB94867A-DAEC-E048-8D16-E26ABE5705D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7678D290-ED9A-ED41-AA5A-CAC2FFC3ADFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="51">
   <si>
     <t>Hotel ID</t>
   </si>
@@ -31,12 +31,6 @@
     <t>RNS Flag</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Room Type Name</t>
-  </si>
-  <si>
     <t>Mauna Lani Point E102</t>
   </si>
   <si>
@@ -169,7 +163,16 @@
     <t>Mauna Lani Point G202</t>
   </si>
   <si>
-    <t>RoomTypeName</t>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>RNS Room Type</t>
+  </si>
+  <si>
+    <t>RNS Custom Label</t>
+  </si>
+  <si>
+    <t>Room</t>
   </si>
 </sst>
 </file>
@@ -558,10 +561,11 @@
   <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
-    <col min="4" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -575,10 +579,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -589,13 +593,13 @@
         <v>327600509</v>
       </c>
       <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -606,13 +610,13 @@
         <v>327600806</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -623,13 +627,13 @@
         <v>327600808</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -640,13 +644,13 @@
         <v>327600809</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -657,13 +661,13 @@
         <v>327600515</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -674,13 +678,13 @@
         <v>327600517</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -691,13 +695,13 @@
         <v>327600518</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -708,13 +712,13 @@
         <v>327600521</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -725,13 +729,13 @@
         <v>327600793</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -742,13 +746,13 @@
         <v>327600503</v>
       </c>
       <c r="C11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -759,13 +763,13 @@
         <v>327600527</v>
       </c>
       <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -776,13 +780,13 @@
         <v>327600529</v>
       </c>
       <c r="C13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -793,13 +797,13 @@
         <v>327600502</v>
       </c>
       <c r="C14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -810,13 +814,13 @@
         <v>327600504</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -827,13 +831,13 @@
         <v>327600505</v>
       </c>
       <c r="C16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -844,13 +848,13 @@
         <v>327600506</v>
       </c>
       <c r="C17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -861,13 +865,13 @@
         <v>327600533</v>
       </c>
       <c r="C18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -878,13 +882,13 @@
         <v>327600535</v>
       </c>
       <c r="C19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -895,13 +899,13 @@
         <v>327600537</v>
       </c>
       <c r="C20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>23</v>
+        <v>47</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -912,13 +916,13 @@
         <v>327600538</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -929,13 +933,13 @@
         <v>327600795</v>
       </c>
       <c r="C22" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -946,13 +950,13 @@
         <v>327600798</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -963,13 +967,13 @@
         <v>327600801</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -980,13 +984,13 @@
         <v>327600794</v>
       </c>
       <c r="C25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>28</v>
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -997,13 +1001,13 @@
         <v>327600791</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>47</v>
+      </c>
+      <c r="D26" t="s">
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1014,13 +1018,13 @@
         <v>327600792</v>
       </c>
       <c r="C27" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1031,13 +1035,13 @@
         <v>327600810</v>
       </c>
       <c r="C28" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
+      </c>
+      <c r="D28" t="s">
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1048,13 +1052,13 @@
         <v>327600811</v>
       </c>
       <c r="C29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -1065,13 +1069,13 @@
         <v>327600789</v>
       </c>
       <c r="C30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1082,13 +1086,13 @@
         <v>327600524</v>
       </c>
       <c r="C31" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1099,13 +1103,13 @@
         <v>327600532</v>
       </c>
       <c r="C32" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="D32" t="s">
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1116,13 +1120,13 @@
         <v>327600526</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1133,13 +1137,13 @@
         <v>327600513</v>
       </c>
       <c r="C34" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1150,13 +1154,13 @@
         <v>327600523</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="D35" t="s">
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1167,13 +1171,13 @@
         <v>327600507</v>
       </c>
       <c r="C36" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1184,13 +1188,13 @@
         <v>327600511</v>
       </c>
       <c r="C37" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1201,13 +1205,13 @@
         <v>327600508</v>
       </c>
       <c r="C38" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="D38" t="s">
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1218,13 +1222,13 @@
         <v>327600516</v>
       </c>
       <c r="C39" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1235,13 +1239,13 @@
         <v>327600531</v>
       </c>
       <c r="C40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1252,13 +1256,13 @@
         <v>327600510</v>
       </c>
       <c r="C41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1269,13 +1273,13 @@
         <v>327600803</v>
       </c>
       <c r="C42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1286,13 +1290,13 @@
         <v>327600804</v>
       </c>
       <c r="C43" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1303,13 +1307,13 @@
         <v>327600805</v>
       </c>
       <c r="C44" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>47</v>
+        <v>47</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1320,13 +1324,13 @@
         <v>327600807</v>
       </c>
       <c r="C45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1337,13 +1341,13 @@
         <v>327600803</v>
       </c>
       <c r="C46" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="D46" t="s">
+        <v>50</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1354,13 +1358,13 @@
         <v>327600804</v>
       </c>
       <c r="C47" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="D47" t="s">
+        <v>50</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1371,13 +1375,13 @@
         <v>327600798</v>
       </c>
       <c r="C48" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
+      </c>
+      <c r="D48" t="s">
+        <v>50</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1388,13 +1392,13 @@
         <v>327600801</v>
       </c>
       <c r="C49" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
+      </c>
+      <c r="D49" t="s">
+        <v>50</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1405,13 +1409,13 @@
         <v>327600792</v>
       </c>
       <c r="C50" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="D50" t="s">
+        <v>50</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -1422,13 +1426,13 @@
         <v>327600794</v>
       </c>
       <c r="C51" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>28</v>
+        <v>47</v>
+      </c>
+      <c r="D51" t="s">
+        <v>50</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1439,13 +1443,13 @@
         <v>327600795</v>
       </c>
       <c r="C52" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>25</v>
+        <v>47</v>
+      </c>
+      <c r="D52" t="s">
+        <v>50</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1456,13 +1460,13 @@
         <v>327600510</v>
       </c>
       <c r="C53" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="D53" t="s">
+        <v>50</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1473,13 +1477,13 @@
         <v>327600523</v>
       </c>
       <c r="C54" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="D54" t="s">
+        <v>50</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1490,13 +1494,13 @@
         <v>327600507</v>
       </c>
       <c r="C55" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="D55" t="s">
+        <v>50</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1507,13 +1511,13 @@
         <v>327600531</v>
       </c>
       <c r="C56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="D56" t="s">
+        <v>50</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1524,13 +1528,13 @@
         <v>327600516</v>
       </c>
       <c r="C57" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="D57" t="s">
+        <v>50</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1541,13 +1545,13 @@
         <v>327600805</v>
       </c>
       <c r="C58" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>47</v>
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>50</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -1558,13 +1562,13 @@
         <v>327600807</v>
       </c>
       <c r="C59" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="D59" t="s">
+        <v>50</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -1575,13 +1579,13 @@
         <v>327600521</v>
       </c>
       <c r="C60" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>12</v>
+        <v>47</v>
+      </c>
+      <c r="D60" t="s">
+        <v>50</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -1592,13 +1596,13 @@
         <v>327600509</v>
       </c>
       <c r="C61" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" t="s">
+        <v>50</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -1609,13 +1613,13 @@
         <v>327600518</v>
       </c>
       <c r="C62" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>11</v>
+        <v>47</v>
+      </c>
+      <c r="D62" t="s">
+        <v>50</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -1626,13 +1630,13 @@
         <v>327600515</v>
       </c>
       <c r="C63" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
+      </c>
+      <c r="D63" t="s">
+        <v>50</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -1643,13 +1647,13 @@
         <v>327600517</v>
       </c>
       <c r="C64" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>10</v>
+        <v>47</v>
+      </c>
+      <c r="D64" t="s">
+        <v>50</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -1660,13 +1664,13 @@
         <v>327600793</v>
       </c>
       <c r="C65" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
+      </c>
+      <c r="D65" t="s">
+        <v>50</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -1677,13 +1681,13 @@
         <v>327600791</v>
       </c>
       <c r="C66" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>29</v>
+        <v>47</v>
+      </c>
+      <c r="D66" t="s">
+        <v>50</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -1694,13 +1698,13 @@
         <v>327600811</v>
       </c>
       <c r="C67" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="D67" t="s">
+        <v>50</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -1711,13 +1715,13 @@
         <v>327600789</v>
       </c>
       <c r="C68" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
+      </c>
+      <c r="D68" t="s">
+        <v>50</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -1728,13 +1732,13 @@
         <v>327600809</v>
       </c>
       <c r="C69" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
+      </c>
+      <c r="D69" t="s">
+        <v>50</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -1745,13 +1749,13 @@
         <v>327600810</v>
       </c>
       <c r="C70" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
+      </c>
+      <c r="D70" t="s">
+        <v>50</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -1762,13 +1766,13 @@
         <v>327600806</v>
       </c>
       <c r="C71" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>6</v>
+        <v>47</v>
+      </c>
+      <c r="D71" t="s">
+        <v>50</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -1779,13 +1783,13 @@
         <v>327600808</v>
       </c>
       <c r="C72" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
+      </c>
+      <c r="D72" t="s">
+        <v>50</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -1796,13 +1800,13 @@
         <v>327600529</v>
       </c>
       <c r="C73" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
+      </c>
+      <c r="D73" t="s">
+        <v>50</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -1813,13 +1817,13 @@
         <v>327600503</v>
       </c>
       <c r="C74" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="D74" t="s">
+        <v>50</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -1830,13 +1834,13 @@
         <v>327600527</v>
       </c>
       <c r="C75" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="D75" t="s">
+        <v>50</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -1847,13 +1851,13 @@
         <v>327600513</v>
       </c>
       <c r="C76" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
+      </c>
+      <c r="D76" t="s">
+        <v>50</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -1864,13 +1868,13 @@
         <v>327600533</v>
       </c>
       <c r="C77" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>21</v>
+        <v>47</v>
+      </c>
+      <c r="D77" t="s">
+        <v>50</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -1881,13 +1885,13 @@
         <v>327600526</v>
       </c>
       <c r="C78" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
+      </c>
+      <c r="D78" t="s">
+        <v>50</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -1898,13 +1902,13 @@
         <v>327600524</v>
       </c>
       <c r="C79" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
+      </c>
+      <c r="D79" t="s">
+        <v>50</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -1915,13 +1919,13 @@
         <v>327600532</v>
       </c>
       <c r="C80" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="D80" t="s">
+        <v>50</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -1932,13 +1936,13 @@
         <v>327600511</v>
       </c>
       <c r="C81" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
+      </c>
+      <c r="D81" t="s">
+        <v>50</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -1949,13 +1953,13 @@
         <v>327600508</v>
       </c>
       <c r="C82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="D82" t="s">
+        <v>50</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -1966,13 +1970,13 @@
         <v>327600506</v>
       </c>
       <c r="C83" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
+      </c>
+      <c r="D83" t="s">
+        <v>50</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -1983,13 +1987,13 @@
         <v>327600504</v>
       </c>
       <c r="C84" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>18</v>
+        <v>47</v>
+      </c>
+      <c r="D84" t="s">
+        <v>50</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -2000,13 +2004,13 @@
         <v>327600505</v>
       </c>
       <c r="C85" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
+      </c>
+      <c r="D85" t="s">
+        <v>50</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -2017,13 +2021,13 @@
         <v>327600538</v>
       </c>
       <c r="C86" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
+      </c>
+      <c r="D86" t="s">
+        <v>50</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -2034,13 +2038,13 @@
         <v>327600502</v>
       </c>
       <c r="C87" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="D87" t="s">
+        <v>50</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -2051,13 +2055,13 @@
         <v>327600535</v>
       </c>
       <c r="C88" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
+      </c>
+      <c r="D88" t="s">
+        <v>50</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -2068,13 +2072,13 @@
         <v>327600537</v>
       </c>
       <c r="C89" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>23</v>
+        <v>47</v>
+      </c>
+      <c r="D89" t="s">
+        <v>50</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
